--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_10.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_10.xlsx
@@ -480,25 +480,25 @@
         <v>45931</v>
       </c>
       <c r="B5" t="n">
-        <v>1395.94</v>
+        <v>1542.48</v>
       </c>
       <c r="C5" t="n">
-        <v>22.14</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>1016.42</v>
+        <v>1128.06</v>
       </c>
       <c r="E5" t="n">
-        <v>267.68</v>
+        <v>312.2</v>
       </c>
       <c r="F5" t="n">
-        <v>2035</v>
+        <v>1309</v>
       </c>
       <c r="G5" t="n">
-        <v>386400</v>
+        <v>421457</v>
       </c>
       <c r="H5" t="n">
-        <v>62444</v>
+        <v>67781</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45932</v>
       </c>
       <c r="B6" t="n">
-        <v>1302.29</v>
+        <v>1500.88</v>
       </c>
       <c r="C6" t="n">
-        <v>21.39</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>938.9400000000001</v>
+        <v>1093.58</v>
       </c>
       <c r="E6" t="n">
-        <v>251.94</v>
+        <v>295.57</v>
       </c>
       <c r="F6" t="n">
-        <v>1627</v>
+        <v>1470</v>
       </c>
       <c r="G6" t="n">
-        <v>326641</v>
+        <v>421185</v>
       </c>
       <c r="H6" t="n">
-        <v>59889</v>
+        <v>67524</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45933</v>
       </c>
       <c r="B7" t="n">
-        <v>650.8099999999999</v>
+        <v>704.6</v>
       </c>
       <c r="C7" t="n">
-        <v>10.2</v>
+        <v>11.23</v>
       </c>
       <c r="D7" t="n">
-        <v>467.87</v>
+        <v>513.0599999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>128.03</v>
+        <v>140.82</v>
       </c>
       <c r="F7" t="n">
-        <v>2802</v>
+        <v>769</v>
       </c>
       <c r="G7" t="n">
-        <v>175392</v>
+        <v>197155</v>
       </c>
       <c r="H7" t="n">
-        <v>28171</v>
+        <v>32794</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45934</v>
       </c>
       <c r="B8" t="n">
-        <v>1362.94</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>21.72</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>977.26</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>270.34</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2396</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>373463</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>63310</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45935</v>
       </c>
       <c r="B9" t="n">
-        <v>1486.59</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1082.64</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>295.43</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2540</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>406460</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>70713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45936</v>
       </c>
       <c r="B10" t="n">
-        <v>1398.12</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.53</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1011.33</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>280.26</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1937</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>365579</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>64078</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45937</v>
       </c>
       <c r="B11" t="n">
-        <v>1153.89</v>
+        <v>1552.06</v>
       </c>
       <c r="C11" t="n">
-        <v>19.02</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>841.02</v>
+        <v>1121.55</v>
       </c>
       <c r="E11" t="n">
-        <v>229.06</v>
+        <v>304.68</v>
       </c>
       <c r="F11" t="n">
-        <v>2078</v>
+        <v>1532</v>
       </c>
       <c r="G11" t="n">
-        <v>331381</v>
+        <v>413435</v>
       </c>
       <c r="H11" t="n">
-        <v>55367</v>
+        <v>69790</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45938</v>
       </c>
       <c r="B12" t="n">
-        <v>1347.83</v>
+        <v>1243.24</v>
       </c>
       <c r="C12" t="n">
-        <v>21.14</v>
+        <v>18.72</v>
       </c>
       <c r="D12" t="n">
-        <v>990.9</v>
+        <v>908.95</v>
       </c>
       <c r="E12" t="n">
-        <v>276.4</v>
+        <v>251.55</v>
       </c>
       <c r="F12" t="n">
-        <v>2643</v>
+        <v>1668</v>
       </c>
       <c r="G12" t="n">
-        <v>354847</v>
+        <v>336744</v>
       </c>
       <c r="H12" t="n">
-        <v>59840</v>
+        <v>59936</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45939</v>
       </c>
       <c r="B13" t="n">
-        <v>1017.22</v>
+        <v>1418.4</v>
       </c>
       <c r="C13" t="n">
-        <v>16.54</v>
+        <v>23.68</v>
       </c>
       <c r="D13" t="n">
-        <v>733.3200000000001</v>
+        <v>1032.9</v>
       </c>
       <c r="E13" t="n">
-        <v>200.72</v>
+        <v>268.96</v>
       </c>
       <c r="F13" t="n">
-        <v>2048</v>
+        <v>1346</v>
       </c>
       <c r="G13" t="n">
-        <v>272790</v>
+        <v>386580</v>
       </c>
       <c r="H13" t="n">
-        <v>43496</v>
+        <v>69295</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45940</v>
       </c>
       <c r="B14" t="n">
-        <v>259.98</v>
+        <v>1529.21</v>
       </c>
       <c r="C14" t="n">
-        <v>4.32</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>189.61</v>
+        <v>1100.51</v>
       </c>
       <c r="E14" t="n">
-        <v>53.47</v>
+        <v>318.26</v>
       </c>
       <c r="F14" t="n">
-        <v>548</v>
+        <v>1555</v>
       </c>
       <c r="G14" t="n">
-        <v>80178</v>
+        <v>388495</v>
       </c>
       <c r="H14" t="n">
-        <v>11646</v>
+        <v>71227</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45941</v>
       </c>
       <c r="B15" t="n">
-        <v>1275.1</v>
+        <v>1555.38</v>
       </c>
       <c r="C15" t="n">
-        <v>20.85</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>925.05</v>
+        <v>1125.36</v>
       </c>
       <c r="E15" t="n">
-        <v>256.75</v>
+        <v>313.62</v>
       </c>
       <c r="F15" t="n">
-        <v>2021</v>
+        <v>1495</v>
       </c>
       <c r="G15" t="n">
-        <v>350364</v>
+        <v>397079</v>
       </c>
       <c r="H15" t="n">
-        <v>58123</v>
+        <v>73754</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45942</v>
       </c>
       <c r="B16" t="n">
-        <v>751.99</v>
+        <v>1519.02</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>552.77</v>
+        <v>1104.98</v>
       </c>
       <c r="E16" t="n">
-        <v>150.5</v>
+        <v>297.62</v>
       </c>
       <c r="F16" t="n">
-        <v>1468</v>
+        <v>1643</v>
       </c>
       <c r="G16" t="n">
-        <v>193940</v>
+        <v>393932</v>
       </c>
       <c r="H16" t="n">
-        <v>34539</v>
+        <v>65143</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45943</v>
       </c>
       <c r="B17" t="n">
-        <v>610.47</v>
+        <v>968.83</v>
       </c>
       <c r="C17" t="n">
-        <v>9.77</v>
+        <v>15.67</v>
       </c>
       <c r="D17" t="n">
-        <v>443.31</v>
+        <v>703.04</v>
       </c>
       <c r="E17" t="n">
-        <v>121.55</v>
+        <v>198.18</v>
       </c>
       <c r="F17" t="n">
-        <v>1157</v>
+        <v>1116</v>
       </c>
       <c r="G17" t="n">
-        <v>149116</v>
+        <v>288601</v>
       </c>
       <c r="H17" t="n">
-        <v>27843</v>
+        <v>43333</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45944</v>
       </c>
       <c r="B18" t="n">
-        <v>310.78</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>225.5</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>61.91</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>611</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>96623</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>12748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45945</v>
       </c>
       <c r="B19" t="n">
-        <v>1070.16</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.53</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>779.78</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>208.86</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2188</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>300107</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>50188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45946</v>
       </c>
       <c r="B20" t="n">
-        <v>786.11</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>13.52</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>568.42</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>158.75</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1367</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>206532</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>35246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45947</v>
       </c>
       <c r="B21" t="n">
-        <v>942.23</v>
+        <v>1456.75</v>
       </c>
       <c r="C21" t="n">
-        <v>14.28</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>677.24</v>
+        <v>1051</v>
       </c>
       <c r="E21" t="n">
-        <v>187.47</v>
+        <v>290.43</v>
       </c>
       <c r="F21" t="n">
-        <v>1738</v>
+        <v>1544</v>
       </c>
       <c r="G21" t="n">
-        <v>242702</v>
+        <v>399523</v>
       </c>
       <c r="H21" t="n">
-        <v>39816</v>
+        <v>68877</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45948</v>
       </c>
       <c r="B22" t="n">
-        <v>1072.38</v>
+        <v>1525.89</v>
       </c>
       <c r="C22" t="n">
-        <v>16.74</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>774.55</v>
+        <v>1096.9</v>
       </c>
       <c r="E22" t="n">
-        <v>211.78</v>
+        <v>307.01</v>
       </c>
       <c r="F22" t="n">
-        <v>2509</v>
+        <v>1459</v>
       </c>
       <c r="G22" t="n">
-        <v>306035</v>
+        <v>415787</v>
       </c>
       <c r="H22" t="n">
-        <v>46787</v>
+        <v>66331</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45949</v>
       </c>
       <c r="B23" t="n">
-        <v>1044.48</v>
+        <v>1585.18</v>
       </c>
       <c r="C23" t="n">
-        <v>17.6</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>753.46</v>
+        <v>1143.47</v>
       </c>
       <c r="E23" t="n">
-        <v>213.67</v>
+        <v>292.18</v>
       </c>
       <c r="F23" t="n">
-        <v>2426</v>
+        <v>1579</v>
       </c>
       <c r="G23" t="n">
-        <v>311501</v>
+        <v>424642</v>
       </c>
       <c r="H23" t="n">
-        <v>46920</v>
+        <v>65793</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45950</v>
       </c>
       <c r="B24" t="n">
-        <v>615.87</v>
+        <v>1556.41</v>
       </c>
       <c r="C24" t="n">
-        <v>9.960000000000001</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>448.9</v>
+        <v>1131.07</v>
       </c>
       <c r="E24" t="n">
-        <v>122.98</v>
+        <v>309.04</v>
       </c>
       <c r="F24" t="n">
-        <v>941</v>
+        <v>1328</v>
       </c>
       <c r="G24" t="n">
-        <v>166001</v>
+        <v>399472</v>
       </c>
       <c r="H24" t="n">
-        <v>28624</v>
+        <v>72425</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45951</v>
       </c>
       <c r="B25" t="n">
-        <v>466.82</v>
+        <v>1468.82</v>
       </c>
       <c r="C25" t="n">
-        <v>7.27</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>338.5</v>
+        <v>1062.14</v>
       </c>
       <c r="E25" t="n">
-        <v>89.47</v>
+        <v>287.74</v>
       </c>
       <c r="F25" t="n">
-        <v>1062</v>
+        <v>1207</v>
       </c>
       <c r="G25" t="n">
-        <v>129616</v>
+        <v>396093</v>
       </c>
       <c r="H25" t="n">
-        <v>20098</v>
+        <v>65927</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45952</v>
       </c>
       <c r="B26" t="n">
-        <v>828.03</v>
+        <v>1221.23</v>
       </c>
       <c r="C26" t="n">
-        <v>13.24</v>
+        <v>21.85</v>
       </c>
       <c r="D26" t="n">
-        <v>597.27</v>
+        <v>883.46</v>
       </c>
       <c r="E26" t="n">
-        <v>163.02</v>
+        <v>242.14</v>
       </c>
       <c r="F26" t="n">
-        <v>1682</v>
+        <v>1127</v>
       </c>
       <c r="G26" t="n">
-        <v>233277</v>
+        <v>322111</v>
       </c>
       <c r="H26" t="n">
-        <v>38490</v>
+        <v>56471</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45953</v>
       </c>
       <c r="B27" t="n">
-        <v>842.27</v>
+        <v>1361.19</v>
       </c>
       <c r="C27" t="n">
-        <v>14.28</v>
+        <v>21.43</v>
       </c>
       <c r="D27" t="n">
-        <v>612.58</v>
+        <v>983.12</v>
       </c>
       <c r="E27" t="n">
-        <v>171.92</v>
+        <v>265.54</v>
       </c>
       <c r="F27" t="n">
-        <v>1633</v>
+        <v>1510</v>
       </c>
       <c r="G27" t="n">
-        <v>245825</v>
+        <v>328875</v>
       </c>
       <c r="H27" t="n">
-        <v>39337</v>
+        <v>58830</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45954</v>
       </c>
       <c r="B28" t="n">
-        <v>259.35</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>187.36</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>51.69</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>80213</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>12058</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45955</v>
       </c>
       <c r="B29" t="n">
-        <v>763.21</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>12.72</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>555.3</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>152.76</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1354</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>204014</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>35618</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45956</v>
       </c>
       <c r="B30" t="n">
-        <v>977.9299999999999</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>16.06</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>708.03</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>192.54</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1552</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>283518</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>43926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45957</v>
       </c>
       <c r="B31" t="n">
-        <v>1330.38</v>
+        <v>1193.18</v>
       </c>
       <c r="C31" t="n">
-        <v>21.58</v>
+        <v>19.58</v>
       </c>
       <c r="D31" t="n">
-        <v>964.5599999999999</v>
+        <v>866.8</v>
       </c>
       <c r="E31" t="n">
-        <v>264.07</v>
+        <v>244.59</v>
       </c>
       <c r="F31" t="n">
-        <v>1684</v>
+        <v>1352</v>
       </c>
       <c r="G31" t="n">
-        <v>385732</v>
+        <v>377248</v>
       </c>
       <c r="H31" t="n">
-        <v>57568</v>
+        <v>57564</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45958</v>
       </c>
       <c r="B32" t="n">
-        <v>704.1</v>
+        <v>1502.67</v>
       </c>
       <c r="C32" t="n">
-        <v>11.33</v>
+        <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>506.51</v>
+        <v>1090.75</v>
       </c>
       <c r="E32" t="n">
-        <v>135.66</v>
+        <v>294.54</v>
       </c>
       <c r="F32" t="n">
-        <v>1365</v>
+        <v>1649</v>
       </c>
       <c r="G32" t="n">
-        <v>185605</v>
+        <v>390404</v>
       </c>
       <c r="H32" t="n">
-        <v>31083</v>
+        <v>70021</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45959</v>
       </c>
       <c r="B33" t="n">
-        <v>722.6900000000001</v>
+        <v>1503.2</v>
       </c>
       <c r="C33" t="n">
-        <v>11.65</v>
+        <v>24</v>
       </c>
       <c r="D33" t="n">
-        <v>522.79</v>
+        <v>1098.25</v>
       </c>
       <c r="E33" t="n">
-        <v>140.69</v>
+        <v>296.08</v>
       </c>
       <c r="F33" t="n">
-        <v>1111</v>
+        <v>1275</v>
       </c>
       <c r="G33" t="n">
-        <v>189135</v>
+        <v>427241</v>
       </c>
       <c r="H33" t="n">
-        <v>34624</v>
+        <v>71236</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45960</v>
       </c>
       <c r="B34" t="n">
-        <v>1405.15</v>
+        <v>1552.24</v>
       </c>
       <c r="C34" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="D34" t="n">
-        <v>1015.18</v>
+        <v>1126.69</v>
       </c>
       <c r="E34" t="n">
-        <v>279.62</v>
+        <v>327.5</v>
       </c>
       <c r="F34" t="n">
-        <v>1966</v>
+        <v>1500</v>
       </c>
       <c r="G34" t="n">
-        <v>376580</v>
+        <v>446170</v>
       </c>
       <c r="H34" t="n">
-        <v>62485</v>
+        <v>70652</v>
       </c>
     </row>
     <row r="35">
@@ -1260,25 +1260,25 @@
         <v>45961</v>
       </c>
       <c r="B35" t="n">
-        <v>576.12</v>
+        <v>608.3</v>
       </c>
       <c r="C35" t="n">
-        <v>9.57</v>
+        <v>10.13</v>
       </c>
       <c r="D35" t="n">
-        <v>417.53</v>
+        <v>440.58</v>
       </c>
       <c r="E35" t="n">
-        <v>116.04</v>
+        <v>119.99</v>
       </c>
       <c r="F35" t="n">
-        <v>1143</v>
+        <v>550</v>
       </c>
       <c r="G35" t="n">
-        <v>159742</v>
+        <v>161255</v>
       </c>
       <c r="H35" t="n">
-        <v>26324</v>
+        <v>28113</v>
       </c>
     </row>
     <row r="37">
@@ -1288,25 +1288,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28731.23</v>
+        <v>30069.16</v>
       </c>
       <c r="C37" t="n">
-        <v>466.34</v>
+        <v>478.19</v>
       </c>
       <c r="D37" t="n">
-        <v>20823.9</v>
+        <v>21806.22</v>
       </c>
       <c r="E37" t="n">
-        <v>5705.029999999999</v>
+        <v>5978.24</v>
       </c>
       <c r="F37" t="n">
-        <v>52094</v>
+        <v>29983</v>
       </c>
       <c r="G37" t="n">
-        <v>7869309</v>
+        <v>8133484</v>
       </c>
       <c r="H37" t="n">
-        <v>1301399</v>
+        <v>1372817</v>
       </c>
     </row>
   </sheetData>

--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_10.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_10.xlsx
@@ -480,25 +480,25 @@
         <v>45931</v>
       </c>
       <c r="B5" t="n">
-        <v>1542.48</v>
+        <v>1412.09</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>1128.06</v>
+        <v>1028.34</v>
       </c>
       <c r="E5" t="n">
-        <v>312.2</v>
+        <v>274.5</v>
       </c>
       <c r="F5" t="n">
-        <v>1309</v>
+        <v>1245</v>
       </c>
       <c r="G5" t="n">
-        <v>421457</v>
+        <v>398640</v>
       </c>
       <c r="H5" t="n">
-        <v>67781</v>
+        <v>63307</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45932</v>
       </c>
       <c r="B6" t="n">
-        <v>1500.88</v>
+        <v>1408.96</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>1093.58</v>
+        <v>1022.21</v>
       </c>
       <c r="E6" t="n">
-        <v>295.57</v>
+        <v>280.19</v>
       </c>
       <c r="F6" t="n">
-        <v>1470</v>
+        <v>1659</v>
       </c>
       <c r="G6" t="n">
-        <v>421185</v>
+        <v>353964</v>
       </c>
       <c r="H6" t="n">
-        <v>67524</v>
+        <v>55898</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45933</v>
       </c>
       <c r="B7" t="n">
-        <v>704.6</v>
+        <v>1307.36</v>
       </c>
       <c r="C7" t="n">
-        <v>11.23</v>
+        <v>22.46</v>
       </c>
       <c r="D7" t="n">
-        <v>513.0599999999999</v>
+        <v>949.3099999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>140.82</v>
+        <v>260.31</v>
       </c>
       <c r="F7" t="n">
-        <v>769</v>
+        <v>1180</v>
       </c>
       <c r="G7" t="n">
-        <v>197155</v>
+        <v>387413</v>
       </c>
       <c r="H7" t="n">
-        <v>32794</v>
+        <v>59305</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45934</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1217.54</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>21.59</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>885.42</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>235.35</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1163</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>344628</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>59231</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45935</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1420.02</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>22.49</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1031.43</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>289.74</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1232</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>389351</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>64733</v>
       </c>
     </row>
     <row r="10">
@@ -636,25 +636,25 @@
         <v>45937</v>
       </c>
       <c r="B11" t="n">
-        <v>1552.06</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1121.55</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>304.68</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1532</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>413435</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>69790</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45938</v>
       </c>
       <c r="B12" t="n">
-        <v>1243.24</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.72</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>908.95</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>251.55</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1668</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>336744</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>59936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45939</v>
       </c>
       <c r="B13" t="n">
-        <v>1418.4</v>
+        <v>1570.07</v>
       </c>
       <c r="C13" t="n">
-        <v>23.68</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>1032.9</v>
+        <v>1137.27</v>
       </c>
       <c r="E13" t="n">
-        <v>268.96</v>
+        <v>309.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1346</v>
+        <v>1336</v>
       </c>
       <c r="G13" t="n">
-        <v>386580</v>
+        <v>464965</v>
       </c>
       <c r="H13" t="n">
-        <v>69295</v>
+        <v>73668</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45940</v>
       </c>
       <c r="B14" t="n">
-        <v>1529.21</v>
+        <v>1608</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>1100.51</v>
+        <v>1167.16</v>
       </c>
       <c r="E14" t="n">
-        <v>318.26</v>
+        <v>320.06</v>
       </c>
       <c r="F14" t="n">
-        <v>1555</v>
+        <v>1651</v>
       </c>
       <c r="G14" t="n">
-        <v>388495</v>
+        <v>419354</v>
       </c>
       <c r="H14" t="n">
-        <v>71227</v>
+        <v>70870</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45941</v>
       </c>
       <c r="B15" t="n">
-        <v>1555.38</v>
+        <v>1559.6</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>1125.36</v>
+        <v>1134.96</v>
       </c>
       <c r="E15" t="n">
-        <v>313.62</v>
+        <v>306.62</v>
       </c>
       <c r="F15" t="n">
-        <v>1495</v>
+        <v>1147</v>
       </c>
       <c r="G15" t="n">
-        <v>397079</v>
+        <v>426180</v>
       </c>
       <c r="H15" t="n">
-        <v>73754</v>
+        <v>70333</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45942</v>
       </c>
       <c r="B16" t="n">
-        <v>1519.02</v>
+        <v>1177.09</v>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>18.61</v>
       </c>
       <c r="D16" t="n">
-        <v>1104.98</v>
+        <v>853.14</v>
       </c>
       <c r="E16" t="n">
-        <v>297.62</v>
+        <v>227.89</v>
       </c>
       <c r="F16" t="n">
-        <v>1643</v>
+        <v>1421</v>
       </c>
       <c r="G16" t="n">
-        <v>393932</v>
+        <v>343317</v>
       </c>
       <c r="H16" t="n">
-        <v>65143</v>
+        <v>53073</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45943</v>
       </c>
       <c r="B17" t="n">
-        <v>968.83</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.67</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>703.04</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>198.18</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1116</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>288601</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>43333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -896,25 +896,25 @@
         <v>45947</v>
       </c>
       <c r="B21" t="n">
-        <v>1456.75</v>
+        <v>1436.27</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>1051</v>
+        <v>1037.13</v>
       </c>
       <c r="E21" t="n">
-        <v>290.43</v>
+        <v>288.09</v>
       </c>
       <c r="F21" t="n">
-        <v>1544</v>
+        <v>1492</v>
       </c>
       <c r="G21" t="n">
-        <v>399523</v>
+        <v>380761</v>
       </c>
       <c r="H21" t="n">
-        <v>68877</v>
+        <v>63681</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45948</v>
       </c>
       <c r="B22" t="n">
-        <v>1525.89</v>
+        <v>1390.19</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>22.14</v>
       </c>
       <c r="D22" t="n">
-        <v>1096.9</v>
+        <v>1009.14</v>
       </c>
       <c r="E22" t="n">
-        <v>307.01</v>
+        <v>275.3</v>
       </c>
       <c r="F22" t="n">
-        <v>1459</v>
+        <v>1379</v>
       </c>
       <c r="G22" t="n">
-        <v>415787</v>
+        <v>353199</v>
       </c>
       <c r="H22" t="n">
-        <v>66331</v>
+        <v>63296</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45949</v>
       </c>
       <c r="B23" t="n">
-        <v>1585.18</v>
+        <v>1516.83</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>1143.47</v>
+        <v>1103.68</v>
       </c>
       <c r="E23" t="n">
-        <v>292.18</v>
+        <v>292.23</v>
       </c>
       <c r="F23" t="n">
-        <v>1579</v>
+        <v>1219</v>
       </c>
       <c r="G23" t="n">
-        <v>424642</v>
+        <v>427339</v>
       </c>
       <c r="H23" t="n">
-        <v>65793</v>
+        <v>70090</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45950</v>
       </c>
       <c r="B24" t="n">
-        <v>1556.41</v>
+        <v>1446.06</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>1131.07</v>
+        <v>1044.14</v>
       </c>
       <c r="E24" t="n">
-        <v>309.04</v>
+        <v>297.51</v>
       </c>
       <c r="F24" t="n">
-        <v>1328</v>
+        <v>1109</v>
       </c>
       <c r="G24" t="n">
-        <v>399472</v>
+        <v>392603</v>
       </c>
       <c r="H24" t="n">
-        <v>72425</v>
+        <v>68548</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45951</v>
       </c>
       <c r="B25" t="n">
-        <v>1468.82</v>
+        <v>1568.05</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>1062.14</v>
+        <v>1123.57</v>
       </c>
       <c r="E25" t="n">
-        <v>287.74</v>
+        <v>321.79</v>
       </c>
       <c r="F25" t="n">
-        <v>1207</v>
+        <v>1800</v>
       </c>
       <c r="G25" t="n">
-        <v>396093</v>
+        <v>384018</v>
       </c>
       <c r="H25" t="n">
-        <v>65927</v>
+        <v>71010</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45952</v>
       </c>
       <c r="B26" t="n">
-        <v>1221.23</v>
+        <v>1488.66</v>
       </c>
       <c r="C26" t="n">
-        <v>21.85</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>883.46</v>
+        <v>1077.93</v>
       </c>
       <c r="E26" t="n">
-        <v>242.14</v>
+        <v>303.09</v>
       </c>
       <c r="F26" t="n">
-        <v>1127</v>
+        <v>1278</v>
       </c>
       <c r="G26" t="n">
-        <v>322111</v>
+        <v>389230</v>
       </c>
       <c r="H26" t="n">
-        <v>56471</v>
+        <v>66087</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45953</v>
       </c>
       <c r="B27" t="n">
-        <v>1361.19</v>
+        <v>754.77</v>
       </c>
       <c r="C27" t="n">
-        <v>21.43</v>
+        <v>11.81</v>
       </c>
       <c r="D27" t="n">
-        <v>983.12</v>
+        <v>549.33</v>
       </c>
       <c r="E27" t="n">
-        <v>265.54</v>
+        <v>151.09</v>
       </c>
       <c r="F27" t="n">
-        <v>1510</v>
+        <v>958</v>
       </c>
       <c r="G27" t="n">
-        <v>328875</v>
+        <v>202246</v>
       </c>
       <c r="H27" t="n">
-        <v>58830</v>
+        <v>34498</v>
       </c>
     </row>
     <row r="28">
@@ -1156,25 +1156,25 @@
         <v>45957</v>
       </c>
       <c r="B31" t="n">
-        <v>1193.18</v>
+        <v>1419.11</v>
       </c>
       <c r="C31" t="n">
-        <v>19.58</v>
+        <v>22.88</v>
       </c>
       <c r="D31" t="n">
-        <v>866.8</v>
+        <v>1028.96</v>
       </c>
       <c r="E31" t="n">
-        <v>244.59</v>
+        <v>278.07</v>
       </c>
       <c r="F31" t="n">
-        <v>1352</v>
+        <v>1009</v>
       </c>
       <c r="G31" t="n">
-        <v>377248</v>
+        <v>421042</v>
       </c>
       <c r="H31" t="n">
-        <v>57564</v>
+        <v>68988</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45958</v>
       </c>
       <c r="B32" t="n">
-        <v>1502.67</v>
+        <v>1304.34</v>
       </c>
       <c r="C32" t="n">
-        <v>24</v>
+        <v>21.17</v>
       </c>
       <c r="D32" t="n">
-        <v>1090.75</v>
+        <v>943.4</v>
       </c>
       <c r="E32" t="n">
-        <v>294.54</v>
+        <v>261.37</v>
       </c>
       <c r="F32" t="n">
-        <v>1649</v>
+        <v>997</v>
       </c>
       <c r="G32" t="n">
-        <v>390404</v>
+        <v>332931</v>
       </c>
       <c r="H32" t="n">
-        <v>70021</v>
+        <v>57942</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45959</v>
       </c>
       <c r="B33" t="n">
-        <v>1503.2</v>
+        <v>1411.44</v>
       </c>
       <c r="C33" t="n">
-        <v>24</v>
+        <v>23.39</v>
       </c>
       <c r="D33" t="n">
-        <v>1098.25</v>
+        <v>1023.57</v>
       </c>
       <c r="E33" t="n">
-        <v>296.08</v>
+        <v>277.89</v>
       </c>
       <c r="F33" t="n">
-        <v>1275</v>
+        <v>1403</v>
       </c>
       <c r="G33" t="n">
-        <v>427241</v>
+        <v>357768</v>
       </c>
       <c r="H33" t="n">
-        <v>71236</v>
+        <v>58536</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45960</v>
       </c>
       <c r="B34" t="n">
-        <v>1552.24</v>
+        <v>1552.41</v>
       </c>
       <c r="C34" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="D34" t="n">
-        <v>1126.69</v>
+        <v>1137.68</v>
       </c>
       <c r="E34" t="n">
-        <v>327.5</v>
+        <v>322.41</v>
       </c>
       <c r="F34" t="n">
-        <v>1500</v>
+        <v>1268</v>
       </c>
       <c r="G34" t="n">
-        <v>446170</v>
+        <v>400147</v>
       </c>
       <c r="H34" t="n">
-        <v>70652</v>
+        <v>71034</v>
       </c>
     </row>
     <row r="35">
@@ -1260,25 +1260,25 @@
         <v>45961</v>
       </c>
       <c r="B35" t="n">
-        <v>608.3</v>
+        <v>626.16</v>
       </c>
       <c r="C35" t="n">
         <v>10.13</v>
       </c>
       <c r="D35" t="n">
-        <v>440.58</v>
+        <v>458.32</v>
       </c>
       <c r="E35" t="n">
-        <v>119.99</v>
+        <v>126.77</v>
       </c>
       <c r="F35" t="n">
-        <v>550</v>
+        <v>713</v>
       </c>
       <c r="G35" t="n">
-        <v>161255</v>
+        <v>176567</v>
       </c>
       <c r="H35" t="n">
-        <v>28113</v>
+        <v>28810</v>
       </c>
     </row>
     <row r="37">
@@ -1288,25 +1288,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>30069.16</v>
+        <v>28595.02</v>
       </c>
       <c r="C37" t="n">
-        <v>478.19</v>
+        <v>460.67</v>
       </c>
       <c r="D37" t="n">
-        <v>21806.22</v>
+        <v>20746.09</v>
       </c>
       <c r="E37" t="n">
-        <v>5978.24</v>
+        <v>5699.57</v>
       </c>
       <c r="F37" t="n">
-        <v>29983</v>
+        <v>26659</v>
       </c>
       <c r="G37" t="n">
-        <v>8133484</v>
+        <v>7745663</v>
       </c>
       <c r="H37" t="n">
-        <v>1372817</v>
+        <v>1292938</v>
       </c>
     </row>
   </sheetData>
